--- a/Website/static/downloads/showcase/workflows/excel-object-export/example.xlsx
+++ b/Website/static/downloads/showcase/workflows/excel-object-export/example.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <x:si>
     <x:t>AssetTag</x:t>
   </x:si>
@@ -22,9 +22,15 @@
     <x:t>AssignedTeam</x:t>
   </x:si>
   <x:si>
+    <x:t>PurchaseDate</x:t>
+  </x:si>
+  <x:si>
     <x:t>PurchaseCost</x:t>
   </x:si>
   <x:si>
+    <x:t>Status</x:t>
+  </x:si>
+  <x:si>
     <x:t>NW-1042</x:t>
   </x:si>
   <x:si>
@@ -34,6 +40,9 @@
     <x:t>Delivery</x:t>
   </x:si>
   <x:si>
+    <x:t>In use</x:t>
+  </x:si>
+  <x:si>
     <x:t>NW-1043</x:t>
   </x:si>
   <x:si>
@@ -52,6 +61,9 @@
     <x:t>Engineering</x:t>
   </x:si>
   <x:si>
+    <x:t>In stock</x:t>
+  </x:si>
+  <x:si>
     <x:t>NW-1045</x:t>
   </x:si>
   <x:si>
@@ -62,14 +74,37 @@
   </x:si>
   <x:si>
     <x:t>Tablet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>In repair</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NW-1047</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NW-1048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NW-1049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NW-1050</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NW-1051</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <x:numFmts count="3">
+    <x:numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
+    <x:numFmt numFmtId="165" formatCode="d mmm yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
   <x:fonts count="1">
     <x:font>
@@ -89,11 +124,13 @@
     <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <x:xf/>
   </x:cellStyleXfs>
-  <x:cellXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <x:cellXfs count="4">
+    <x:xf/>
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <x:xf numFmtId="166" applyNumberFormat="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -104,13 +141,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Assets" displayName="Assets" ref="A1:D6" headerRowCount="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:D6"/>
-  <x:tableColumns count="4">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Assets" displayName="Assets" ref="A1:F11" headerRowCount="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:F11"/>
+  <x:tableColumns count="6">
     <x:tableColumn id="1" name="AssetTag"/>
     <x:tableColumn id="2" name="Category"/>
     <x:tableColumn id="3" name="AssignedTeam"/>
-    <x:tableColumn id="4" name="PurchaseCost"/>
+    <x:tableColumn id="4" name="PurchaseDate"/>
+    <x:tableColumn id="5" name="PurchaseCost"/>
+    <x:tableColumn id="6" name="Status"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -118,12 +157,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:F11"/>
   <cols>
-    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -139,75 +180,211 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2">
+        <v>46034</v>
+      </c>
+      <c r="E2" s="3">
         <v>1240</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2">
+        <v>46034</v>
+      </c>
+      <c r="E3" s="3">
         <v>320</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2">
+        <v>46056</v>
+      </c>
+      <c r="E4" s="3">
         <v>185</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="1">
+        <v>18</v>
+      </c>
+      <c r="D5" s="2">
+        <v>46070</v>
+      </c>
+      <c r="E5" s="3">
         <v>1390</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2">
+        <v>46083</v>
+      </c>
+      <c r="E6" s="3">
+        <v>680</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="2">
+        <v>46090</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1240</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="2">
+        <v>46104</v>
+      </c>
+      <c r="E8" s="3">
+        <v>320</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2">
+        <v>46118</v>
+      </c>
+      <c r="E9" s="3">
+        <v>540</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="2">
+        <v>46118</v>
+      </c>
+      <c r="E10" s="3">
+        <v>185</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D11" s="2">
+        <v>46132</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1590</v>
+      </c>
+      <c r="F11" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="1">
-        <v>680</v>
       </c>
     </row>
   </sheetData>
